--- a/Excel/liste_groupe_1bis.xlsx
+++ b/Excel/liste_groupe_1bis.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yvesb\Documents\SAPIEN\PowerShell Studio\Files\ASTI\EXCEL\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yvesb\Documents\SAPIEN\PowerShell Studio\Files\ASTI\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E7D6FB20-3E18-4FB7-BE61-5CA4FFFECE48}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F4DFF903-92DB-4B9B-B4A4-4100FEA2AEF5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/Excel/liste_groupe_1bis.xlsx
+++ b/Excel/liste_groupe_1bis.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yvesb\Documents\SAPIEN\PowerShell Studio\Files\ASTI\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F4DFF903-92DB-4B9B-B4A4-4100FEA2AEF5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2794EF30-D085-497C-B6EF-E775C550CEFD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/Excel/liste_groupe_1bis.xlsx
+++ b/Excel/liste_groupe_1bis.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yvesb\Documents\SAPIEN\PowerShell Studio\Files\ASTI\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2794EF30-D085-497C-B6EF-E775C550CEFD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AAEBCA31-F280-4FAF-B68C-819B9E78B1AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/Excel/liste_groupe_1bis.xlsx
+++ b/Excel/liste_groupe_1bis.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yvesb\Documents\SAPIEN\PowerShell Studio\Files\ASTI\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AAEBCA31-F280-4FAF-B68C-819B9E78B1AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{03E04D06-94B2-4807-90DB-6B6DD8A07C2A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/Excel/liste_groupe_1bis.xlsx
+++ b/Excel/liste_groupe_1bis.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yvesb\Documents\SAPIEN\PowerShell Studio\Files\ASTI\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{03E04D06-94B2-4807-90DB-6B6DD8A07C2A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{650595D5-D2BD-4281-BBD7-26D86EDCD19B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/Excel/liste_groupe_1bis.xlsx
+++ b/Excel/liste_groupe_1bis.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yvesb\Documents\SAPIEN\PowerShell Studio\Files\ASTI\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{650595D5-D2BD-4281-BBD7-26D86EDCD19B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{96BB6CFF-BAAC-4736-AE34-981976D4F3BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/Excel/liste_groupe_1bis.xlsx
+++ b/Excel/liste_groupe_1bis.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yvesb\Documents\SAPIEN\PowerShell Studio\Files\ASTI\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{96BB6CFF-BAAC-4736-AE34-981976D4F3BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{23BF06B2-C871-43B1-AD74-A6C035C0F1C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/Excel/liste_groupe_1bis.xlsx
+++ b/Excel/liste_groupe_1bis.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yvesb\Documents\SAPIEN\PowerShell Studio\Files\ASTI\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{23BF06B2-C871-43B1-AD74-A6C035C0F1C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8CC37D8A-1B7A-4A8B-894C-EDACBADFD9F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="7995" yWindow="5535" windowWidth="28815" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="42">
   <si>
     <t>Période de présence aux cours 2025 - 2026 (01/11/2025)</t>
   </si>
@@ -52,91 +52,82 @@
     <t>DATE DE FIN</t>
   </si>
   <si>
-    <t>AHMED</t>
-  </si>
-  <si>
-    <t>Ibrahim</t>
+    <t>AHMED MOHAMED OSMAN</t>
+  </si>
+  <si>
+    <t>Monira</t>
+  </si>
+  <si>
+    <t>01/01/1987</t>
+  </si>
+  <si>
+    <t>Soudan</t>
+  </si>
+  <si>
+    <t>F</t>
+  </si>
+  <si>
+    <t>25/09/2025</t>
   </si>
   <si>
     <t>01/01/1900</t>
   </si>
   <si>
-    <t>N/A</t>
+    <t>MPUTU</t>
+  </si>
+  <si>
+    <t>Bella</t>
+  </si>
+  <si>
+    <t>20/05/1998</t>
+  </si>
+  <si>
+    <t>RDC</t>
+  </si>
+  <si>
+    <t>04/11/2025</t>
+  </si>
+  <si>
+    <t>PETROSYAN</t>
+  </si>
+  <si>
+    <t>Anna</t>
+  </si>
+  <si>
+    <t>07/10/1992</t>
+  </si>
+  <si>
+    <t>Arménie</t>
+  </si>
+  <si>
+    <t>20/03/2025</t>
+  </si>
+  <si>
+    <t>POGHOSYAN</t>
+  </si>
+  <si>
+    <t>Gayane</t>
+  </si>
+  <si>
+    <t>25/09/1960</t>
+  </si>
+  <si>
+    <t>27/09/2023</t>
+  </si>
+  <si>
+    <t>SAYED</t>
+  </si>
+  <si>
+    <t>Mohammad</t>
+  </si>
+  <si>
+    <t>05/08/1989</t>
+  </si>
+  <si>
+    <t>Allemagne</t>
   </si>
   <si>
     <t>M</t>
-  </si>
-  <si>
-    <t>AHMED MOHAMED OSMAN</t>
-  </si>
-  <si>
-    <t>Monira</t>
-  </si>
-  <si>
-    <t>01/01/1987</t>
-  </si>
-  <si>
-    <t>Soudan</t>
-  </si>
-  <si>
-    <t>F</t>
-  </si>
-  <si>
-    <t>25/09/2025</t>
-  </si>
-  <si>
-    <t>MPUTU</t>
-  </si>
-  <si>
-    <t>Bella</t>
-  </si>
-  <si>
-    <t>20/05/1998</t>
-  </si>
-  <si>
-    <t>RDC</t>
-  </si>
-  <si>
-    <t>04/11/2025</t>
-  </si>
-  <si>
-    <t>PETROSYAN</t>
-  </si>
-  <si>
-    <t>Anna</t>
-  </si>
-  <si>
-    <t>07/10/1992</t>
-  </si>
-  <si>
-    <t>Arménie</t>
-  </si>
-  <si>
-    <t>20/03/2025</t>
-  </si>
-  <si>
-    <t>POGHOSYAN</t>
-  </si>
-  <si>
-    <t>Gayane</t>
-  </si>
-  <si>
-    <t>25/09/1960</t>
-  </si>
-  <si>
-    <t>27/09/2023</t>
-  </si>
-  <si>
-    <t>SAYED</t>
-  </si>
-  <si>
-    <t>Mohammad</t>
-  </si>
-  <si>
-    <t>05/08/1989</t>
-  </si>
-  <si>
-    <t>Allemagne</t>
   </si>
   <si>
     <t>16/09/2025</t>
@@ -715,10 +706,10 @@
         <v>13</v>
       </c>
       <c r="G4" s="13" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="39.950000000000003" customHeight="1">
@@ -726,25 +717,25 @@
         <v>2</v>
       </c>
       <c r="B5" s="9" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C5" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="D5" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="F5" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="G5" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="H5" s="2" t="s">
         <v>15</v>
-      </c>
-      <c r="D5" s="13" t="s">
-        <v>16</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="F5" s="13" t="s">
-        <v>18</v>
-      </c>
-      <c r="G5" s="13" t="s">
-        <v>19</v>
-      </c>
-      <c r="H5" s="2" t="s">
-        <v>11</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="39.950000000000003" customHeight="1">
@@ -752,25 +743,25 @@
         <v>3</v>
       </c>
       <c r="B6" s="9" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C6" s="11" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D6" s="13" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F6" s="13" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="G6" s="13" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="39.950000000000003" customHeight="1">
@@ -778,25 +769,25 @@
         <v>4</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C7" s="11" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D7" s="13" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="F7" s="13" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="G7" s="13" t="s">
         <v>29</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
     </row>
     <row r="8" spans="1:8" ht="39.950000000000003" customHeight="1">
@@ -813,16 +804,16 @@
         <v>32</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="F8" s="13" t="s">
-        <v>18</v>
+        <v>34</v>
       </c>
       <c r="G8" s="13" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
     </row>
     <row r="9" spans="1:8" ht="39.950000000000003" customHeight="1">
@@ -830,25 +821,25 @@
         <v>6</v>
       </c>
       <c r="B9" s="9" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="C9" s="11" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D9" s="13" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="F9" s="13" t="s">
         <v>13</v>
       </c>
       <c r="G9" s="13" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
     </row>
     <row r="10" spans="1:8" ht="39.950000000000003" customHeight="1">
@@ -856,7 +847,7 @@
         <v>7</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="C10" s="11" t="s">
         <v>39</v>
@@ -865,43 +856,29 @@
         <v>40</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>37</v>
+        <v>24</v>
       </c>
       <c r="F10" s="13" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="G10" s="13" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
     </row>
     <row r="11" spans="1:8" ht="39.950000000000003" customHeight="1">
-      <c r="A11" s="5">
+      <c r="A11" s="6">
         <v>8</v>
       </c>
-      <c r="B11" s="9" t="s">
-        <v>41</v>
-      </c>
-      <c r="C11" s="11" t="s">
-        <v>42</v>
-      </c>
-      <c r="D11" s="13" t="s">
-        <v>43</v>
-      </c>
-      <c r="E11" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="F11" s="13" t="s">
-        <v>18</v>
-      </c>
-      <c r="G11" s="13" t="s">
-        <v>44</v>
-      </c>
-      <c r="H11" s="2" t="s">
-        <v>11</v>
-      </c>
+      <c r="B11" s="10"/>
+      <c r="C11" s="10"/>
+      <c r="D11" s="14"/>
+      <c r="E11" s="3"/>
+      <c r="F11" s="14"/>
+      <c r="G11" s="14"/>
+      <c r="H11" s="3"/>
     </row>
     <row r="12" spans="1:8" ht="39.950000000000003" customHeight="1">
       <c r="A12" s="6">

--- a/Excel/liste_groupe_1bis.xlsx
+++ b/Excel/liste_groupe_1bis.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yvesb\Documents\SAPIEN\PowerShell Studio\Files\ASTI\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8CC37D8A-1B7A-4A8B-894C-EDACBADFD9F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7238ACC3-2550-4C52-8297-238AFE12BA85}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="7995" yWindow="5535" windowWidth="28815" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/Excel/liste_groupe_1bis.xlsx
+++ b/Excel/liste_groupe_1bis.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yvesb\Documents\SAPIEN\PowerShell Studio\Files\ASTI\Excel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yvesb\AppData\Roaming\ASTI\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7238ACC3-2550-4C52-8297-238AFE12BA85}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{273DD54D-315D-460D-BA45-9BF0FC50E0DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="7995" yWindow="5535" windowWidth="28815" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="8685" yWindow="5535" windowWidth="20115" windowHeight="9945" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="50">
   <si>
     <t>Période de présence aux cours 2025 - 2026 (01/11/2025)</t>
   </si>
@@ -52,6 +52,42 @@
     <t>DATE DE FIN</t>
   </si>
   <si>
+    <t>ABDALLA MIRGHANI</t>
+  </si>
+  <si>
+    <t>Zainab</t>
+  </si>
+  <si>
+    <t>01/01/1964</t>
+  </si>
+  <si>
+    <t>Soudan</t>
+  </si>
+  <si>
+    <t>F</t>
+  </si>
+  <si>
+    <t>19/09/2024</t>
+  </si>
+  <si>
+    <t>01/01/1900</t>
+  </si>
+  <si>
+    <t>AHMED</t>
+  </si>
+  <si>
+    <t>Ibrahim</t>
+  </si>
+  <si>
+    <t>31/12/1899</t>
+  </si>
+  <si>
+    <t>N/A</t>
+  </si>
+  <si>
+    <t>M</t>
+  </si>
+  <si>
     <t>AHMED MOHAMED OSMAN</t>
   </si>
   <si>
@@ -61,18 +97,9 @@
     <t>01/01/1987</t>
   </si>
   <si>
-    <t>Soudan</t>
-  </si>
-  <si>
-    <t>F</t>
-  </si>
-  <si>
     <t>25/09/2025</t>
   </si>
   <si>
-    <t>01/01/1900</t>
-  </si>
-  <si>
     <t>MPUTU</t>
   </si>
   <si>
@@ -82,7 +109,7 @@
     <t>20/05/1998</t>
   </si>
   <si>
-    <t>RDC</t>
+    <t>République démocratique du Congo</t>
   </si>
   <si>
     <t>04/11/2025</t>
@@ -118,25 +145,22 @@
     <t>SAYED</t>
   </si>
   <si>
+    <t>Tamara</t>
+  </si>
+  <si>
+    <t>24/07/1985</t>
+  </si>
+  <si>
+    <t>Allemagne</t>
+  </si>
+  <si>
+    <t>16/09/2025</t>
+  </si>
+  <si>
     <t>Mohammad</t>
   </si>
   <si>
     <t>05/08/1989</t>
-  </si>
-  <si>
-    <t>Allemagne</t>
-  </si>
-  <si>
-    <t>M</t>
-  </si>
-  <si>
-    <t>16/09/2025</t>
-  </si>
-  <si>
-    <t>Tamara</t>
-  </si>
-  <si>
-    <t>24/07/1985</t>
   </si>
   <si>
     <t>YELEJYAN</t>
@@ -632,7 +656,7 @@
     <col min="2" max="2" width="13" style="7" customWidth="1"/>
     <col min="3" max="3" width="15.42578125" style="7" customWidth="1"/>
     <col min="4" max="4" width="11.85546875" style="12" customWidth="1"/>
-    <col min="5" max="5" width="10.7109375" customWidth="1"/>
+    <col min="5" max="5" width="33" customWidth="1"/>
     <col min="6" max="6" width="9.140625" style="12" customWidth="1"/>
     <col min="7" max="7" width="15.140625" style="12" customWidth="1"/>
     <col min="8" max="8" width="12.42578125" customWidth="1"/>
@@ -729,10 +753,10 @@
         <v>19</v>
       </c>
       <c r="F5" s="13" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="G5" s="13" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="H5" s="2" t="s">
         <v>15</v>
@@ -752,13 +776,13 @@
         <v>23</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="F6" s="13" t="s">
         <v>13</v>
       </c>
       <c r="G6" s="13" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H6" s="2" t="s">
         <v>15</v>
@@ -769,16 +793,16 @@
         <v>4</v>
       </c>
       <c r="B7" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="C7" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="C7" s="11" t="s">
+      <c r="D7" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="D7" s="13" t="s">
+      <c r="E7" s="2" t="s">
         <v>28</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>24</v>
       </c>
       <c r="F7" s="13" t="s">
         <v>13</v>
@@ -807,10 +831,10 @@
         <v>33</v>
       </c>
       <c r="F8" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="G8" s="13" t="s">
         <v>34</v>
-      </c>
-      <c r="G8" s="13" t="s">
-        <v>35</v>
       </c>
       <c r="H8" s="2" t="s">
         <v>15</v>
@@ -821,7 +845,7 @@
         <v>6</v>
       </c>
       <c r="B9" s="9" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="C9" s="11" t="s">
         <v>36</v>
@@ -836,7 +860,7 @@
         <v>13</v>
       </c>
       <c r="G9" s="13" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="H9" s="2" t="s">
         <v>15</v>
@@ -847,50 +871,78 @@
         <v>7</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C10" s="11" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D10" s="13" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>24</v>
+        <v>42</v>
       </c>
       <c r="F10" s="13" t="s">
         <v>13</v>
       </c>
       <c r="G10" s="13" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="H10" s="2" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="11" spans="1:8" ht="39.950000000000003" customHeight="1">
-      <c r="A11" s="6">
+      <c r="A11" s="5">
         <v>8</v>
       </c>
-      <c r="B11" s="10"/>
-      <c r="C11" s="10"/>
-      <c r="D11" s="14"/>
-      <c r="E11" s="3"/>
-      <c r="F11" s="14"/>
-      <c r="G11" s="14"/>
-      <c r="H11" s="3"/>
+      <c r="B11" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="C11" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="D11" s="13" t="s">
+        <v>45</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="F11" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="G11" s="13" t="s">
+        <v>43</v>
+      </c>
+      <c r="H11" s="2" t="s">
+        <v>15</v>
+      </c>
     </row>
     <row r="12" spans="1:8" ht="39.950000000000003" customHeight="1">
-      <c r="A12" s="6">
+      <c r="A12" s="5">
         <v>9</v>
       </c>
-      <c r="B12" s="10"/>
-      <c r="C12" s="10"/>
-      <c r="D12" s="14"/>
-      <c r="E12" s="3"/>
-      <c r="F12" s="14"/>
-      <c r="G12" s="14"/>
-      <c r="H12" s="3"/>
+      <c r="B12" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="C12" s="11" t="s">
+        <v>47</v>
+      </c>
+      <c r="D12" s="13" t="s">
+        <v>48</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="F12" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="G12" s="13" t="s">
+        <v>49</v>
+      </c>
+      <c r="H12" s="2" t="s">
+        <v>15</v>
+      </c>
     </row>
     <row r="13" spans="1:8" ht="39.950000000000003" customHeight="1">
       <c r="A13" s="6">

--- a/Excel/liste_groupe_1bis.xlsx
+++ b/Excel/liste_groupe_1bis.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yvesb\AppData\Roaming\ASTI\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{273DD54D-315D-460D-BA45-9BF0FC50E0DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0A63D364-82AD-45BE-94F1-0C5499680AA9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="8685" yWindow="5535" windowWidth="20115" windowHeight="9945" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="49">
   <si>
     <t>Période de présence aux cours 2025 - 2026 (01/11/2025)</t>
   </si>
@@ -79,9 +79,6 @@
     <t>Ibrahim</t>
   </si>
   <si>
-    <t>31/12/1899</t>
-  </si>
-  <si>
     <t>N/A</t>
   </si>
   <si>
@@ -145,22 +142,22 @@
     <t>SAYED</t>
   </si>
   <si>
+    <t>Mohammad</t>
+  </si>
+  <si>
+    <t>05/08/1989</t>
+  </si>
+  <si>
+    <t>Allemagne</t>
+  </si>
+  <si>
+    <t>16/09/2025</t>
+  </si>
+  <si>
     <t>Tamara</t>
   </si>
   <si>
     <t>24/07/1985</t>
-  </si>
-  <si>
-    <t>Allemagne</t>
-  </si>
-  <si>
-    <t>16/09/2025</t>
-  </si>
-  <si>
-    <t>Mohammad</t>
-  </si>
-  <si>
-    <t>05/08/1989</t>
   </si>
   <si>
     <t>YELEJYAN</t>
@@ -747,13 +744,13 @@
         <v>17</v>
       </c>
       <c r="D5" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="E5" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="E5" s="2" t="s">
+      <c r="F5" s="13" t="s">
         <v>19</v>
-      </c>
-      <c r="F5" s="13" t="s">
-        <v>20</v>
       </c>
       <c r="G5" s="13" t="s">
         <v>15</v>
@@ -767,13 +764,13 @@
         <v>3</v>
       </c>
       <c r="B6" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="C6" s="11" t="s">
         <v>21</v>
       </c>
-      <c r="C6" s="11" t="s">
+      <c r="D6" s="13" t="s">
         <v>22</v>
-      </c>
-      <c r="D6" s="13" t="s">
-        <v>23</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>12</v>
@@ -782,7 +779,7 @@
         <v>13</v>
       </c>
       <c r="G6" s="13" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="H6" s="2" t="s">
         <v>15</v>
@@ -793,22 +790,22 @@
         <v>4</v>
       </c>
       <c r="B7" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="C7" s="11" t="s">
         <v>25</v>
       </c>
-      <c r="C7" s="11" t="s">
+      <c r="D7" s="13" t="s">
         <v>26</v>
       </c>
-      <c r="D7" s="13" t="s">
+      <c r="E7" s="2" t="s">
         <v>27</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>28</v>
       </c>
       <c r="F7" s="13" t="s">
         <v>13</v>
       </c>
       <c r="G7" s="13" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="H7" s="2" t="s">
         <v>15</v>
@@ -819,22 +816,22 @@
         <v>5</v>
       </c>
       <c r="B8" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="C8" s="11" t="s">
         <v>30</v>
       </c>
-      <c r="C8" s="11" t="s">
+      <c r="D8" s="13" t="s">
         <v>31</v>
       </c>
-      <c r="D8" s="13" t="s">
+      <c r="E8" s="2" t="s">
         <v>32</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>33</v>
       </c>
       <c r="F8" s="13" t="s">
         <v>13</v>
       </c>
       <c r="G8" s="13" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="H8" s="2" t="s">
         <v>15</v>
@@ -845,22 +842,22 @@
         <v>6</v>
       </c>
       <c r="B9" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="C9" s="11" t="s">
         <v>35</v>
       </c>
-      <c r="C9" s="11" t="s">
+      <c r="D9" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="D9" s="13" t="s">
-        <v>37</v>
-      </c>
       <c r="E9" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F9" s="13" t="s">
         <v>13</v>
       </c>
       <c r="G9" s="13" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="H9" s="2" t="s">
         <v>15</v>
@@ -871,22 +868,22 @@
         <v>7</v>
       </c>
       <c r="B10" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="C10" s="11" t="s">
         <v>39</v>
       </c>
-      <c r="C10" s="11" t="s">
+      <c r="D10" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="D10" s="13" t="s">
+      <c r="E10" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="E10" s="2" t="s">
+      <c r="F10" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="G10" s="13" t="s">
         <v>42</v>
-      </c>
-      <c r="F10" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="G10" s="13" t="s">
-        <v>43</v>
       </c>
       <c r="H10" s="2" t="s">
         <v>15</v>
@@ -897,22 +894,22 @@
         <v>8</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C11" s="11" t="s">
+        <v>43</v>
+      </c>
+      <c r="D11" s="13" t="s">
         <v>44</v>
       </c>
-      <c r="D11" s="13" t="s">
-        <v>45</v>
-      </c>
       <c r="E11" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="F11" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="G11" s="13" t="s">
         <v>42</v>
-      </c>
-      <c r="F11" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="G11" s="13" t="s">
-        <v>43</v>
       </c>
       <c r="H11" s="2" t="s">
         <v>15</v>
@@ -923,22 +920,22 @@
         <v>9</v>
       </c>
       <c r="B12" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="C12" s="11" t="s">
         <v>46</v>
       </c>
-      <c r="C12" s="11" t="s">
+      <c r="D12" s="13" t="s">
         <v>47</v>
       </c>
-      <c r="D12" s="13" t="s">
-        <v>48</v>
-      </c>
       <c r="E12" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F12" s="13" t="s">
         <v>13</v>
       </c>
       <c r="G12" s="13" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="H12" s="2" t="s">
         <v>15</v>

--- a/Excel/liste_groupe_1bis.xlsx
+++ b/Excel/liste_groupe_1bis.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yvesb\AppData\Roaming\ASTI\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0A63D364-82AD-45BE-94F1-0C5499680AA9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{722824CA-D5D1-44C6-9EB7-4F2DC48E26AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="34">
   <si>
     <t>Période de présence aux cours 2025 - 2026 (01/11/2025)</t>
   </si>
@@ -58,7 +58,7 @@
     <t>Zainab</t>
   </si>
   <si>
-    <t>01/01/1964</t>
+    <t/>
   </si>
   <si>
     <t>Soudan</t>
@@ -67,12 +67,6 @@
     <t>F</t>
   </si>
   <si>
-    <t>19/09/2024</t>
-  </si>
-  <si>
-    <t>01/01/1900</t>
-  </si>
-  <si>
     <t>AHMED</t>
   </si>
   <si>
@@ -91,85 +85,46 @@
     <t>Monira</t>
   </si>
   <si>
-    <t>01/01/1987</t>
-  </si>
-  <si>
-    <t>25/09/2025</t>
-  </si>
-  <si>
     <t>MPUTU</t>
   </si>
   <si>
     <t>Bella</t>
   </si>
   <si>
-    <t>20/05/1998</t>
-  </si>
-  <si>
     <t>République démocratique du Congo</t>
   </si>
   <si>
-    <t>04/11/2025</t>
-  </si>
-  <si>
     <t>PETROSYAN</t>
   </si>
   <si>
     <t>Anna</t>
   </si>
   <si>
-    <t>07/10/1992</t>
-  </si>
-  <si>
     <t>Arménie</t>
   </si>
   <si>
-    <t>20/03/2025</t>
-  </si>
-  <si>
     <t>POGHOSYAN</t>
   </si>
   <si>
     <t>Gayane</t>
   </si>
   <si>
-    <t>25/09/1960</t>
-  </si>
-  <si>
-    <t>27/09/2023</t>
-  </si>
-  <si>
     <t>SAYED</t>
   </si>
   <si>
     <t>Mohammad</t>
   </si>
   <si>
-    <t>05/08/1989</t>
-  </si>
-  <si>
     <t>Allemagne</t>
   </si>
   <si>
-    <t>16/09/2025</t>
-  </si>
-  <si>
     <t>Tamara</t>
   </si>
   <si>
-    <t>24/07/1985</t>
-  </si>
-  <si>
     <t>YELEJYAN</t>
   </si>
   <si>
     <t>Gohar</t>
-  </si>
-  <si>
-    <t>20/12/1983</t>
-  </si>
-  <si>
-    <t>03/09/2025</t>
   </si>
 </sst>
 </file>
@@ -727,10 +682,10 @@
         <v>13</v>
       </c>
       <c r="G4" s="13" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="39.950000000000003" customHeight="1">
@@ -738,25 +693,25 @@
         <v>2</v>
       </c>
       <c r="B5" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="C5" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="D5" s="13" t="s">
+        <v>11</v>
+      </c>
+      <c r="E5" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C5" s="11" t="s">
+      <c r="F5" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="D5" s="13" t="s">
-        <v>15</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="F5" s="13" t="s">
-        <v>19</v>
-      </c>
       <c r="G5" s="13" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="39.950000000000003" customHeight="1">
@@ -764,13 +719,13 @@
         <v>3</v>
       </c>
       <c r="B6" s="9" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C6" s="11" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D6" s="13" t="s">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>12</v>
@@ -779,10 +734,10 @@
         <v>13</v>
       </c>
       <c r="G6" s="13" t="s">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="39.950000000000003" customHeight="1">
@@ -790,25 +745,25 @@
         <v>4</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="C7" s="11" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="D7" s="13" t="s">
-        <v>26</v>
+        <v>11</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="F7" s="13" t="s">
         <v>13</v>
       </c>
       <c r="G7" s="13" t="s">
-        <v>28</v>
+        <v>11</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
     </row>
     <row r="8" spans="1:8" ht="39.950000000000003" customHeight="1">
@@ -816,25 +771,25 @@
         <v>5</v>
       </c>
       <c r="B8" s="9" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="C8" s="11" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="D8" s="13" t="s">
-        <v>31</v>
+        <v>11</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="F8" s="13" t="s">
         <v>13</v>
       </c>
       <c r="G8" s="13" t="s">
-        <v>33</v>
+        <v>11</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
     </row>
     <row r="9" spans="1:8" ht="39.950000000000003" customHeight="1">
@@ -842,25 +797,25 @@
         <v>6</v>
       </c>
       <c r="B9" s="9" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="C9" s="11" t="s">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="D9" s="13" t="s">
-        <v>36</v>
+        <v>11</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="F9" s="13" t="s">
         <v>13</v>
       </c>
       <c r="G9" s="13" t="s">
-        <v>37</v>
+        <v>11</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
     </row>
     <row r="10" spans="1:8" ht="39.950000000000003" customHeight="1">
@@ -868,25 +823,25 @@
         <v>7</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="C10" s="11" t="s">
-        <v>39</v>
+        <v>29</v>
       </c>
       <c r="D10" s="13" t="s">
-        <v>40</v>
+        <v>11</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>41</v>
+        <v>30</v>
       </c>
       <c r="F10" s="13" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="G10" s="13" t="s">
-        <v>42</v>
+        <v>11</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
     </row>
     <row r="11" spans="1:8" ht="39.950000000000003" customHeight="1">
@@ -894,25 +849,25 @@
         <v>8</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="C11" s="11" t="s">
-        <v>43</v>
+        <v>31</v>
       </c>
       <c r="D11" s="13" t="s">
-        <v>44</v>
+        <v>11</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>41</v>
+        <v>30</v>
       </c>
       <c r="F11" s="13" t="s">
         <v>13</v>
       </c>
       <c r="G11" s="13" t="s">
-        <v>42</v>
+        <v>11</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
     </row>
     <row r="12" spans="1:8" ht="39.950000000000003" customHeight="1">
@@ -920,25 +875,25 @@
         <v>9</v>
       </c>
       <c r="B12" s="9" t="s">
-        <v>45</v>
+        <v>32</v>
       </c>
       <c r="C12" s="11" t="s">
-        <v>46</v>
+        <v>33</v>
       </c>
       <c r="D12" s="13" t="s">
-        <v>47</v>
+        <v>11</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="F12" s="13" t="s">
         <v>13</v>
       </c>
       <c r="G12" s="13" t="s">
-        <v>48</v>
+        <v>11</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
     </row>
     <row r="13" spans="1:8" ht="39.950000000000003" customHeight="1">

--- a/Excel/liste_groupe_1bis.xlsx
+++ b/Excel/liste_groupe_1bis.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yvesb\AppData\Roaming\ASTI\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{722824CA-D5D1-44C6-9EB7-4F2DC48E26AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{269768CA-5944-4FC2-A137-5E60319619F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/Excel/liste_groupe_1bis.xlsx
+++ b/Excel/liste_groupe_1bis.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yvesb\AppData\Roaming\ASTI\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{269768CA-5944-4FC2-A137-5E60319619F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{88A4E34A-C548-48E4-BAA3-13750B035B6E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="49">
   <si>
     <t>Période de présence aux cours 2025 - 2026 (01/11/2025)</t>
   </si>
@@ -58,7 +58,7 @@
     <t>Zainab</t>
   </si>
   <si>
-    <t/>
+    <t>01/01/1964</t>
   </si>
   <si>
     <t>Soudan</t>
@@ -67,6 +67,12 @@
     <t>F</t>
   </si>
   <si>
+    <t>19/09/2024</t>
+  </si>
+  <si>
+    <t>01/01/1900</t>
+  </si>
+  <si>
     <t>AHMED</t>
   </si>
   <si>
@@ -85,46 +91,85 @@
     <t>Monira</t>
   </si>
   <si>
+    <t>01/01/1987</t>
+  </si>
+  <si>
+    <t>25/09/2025</t>
+  </si>
+  <si>
     <t>MPUTU</t>
   </si>
   <si>
     <t>Bella</t>
   </si>
   <si>
+    <t>20/05/1998</t>
+  </si>
+  <si>
     <t>République démocratique du Congo</t>
   </si>
   <si>
+    <t>04/11/2025</t>
+  </si>
+  <si>
     <t>PETROSYAN</t>
   </si>
   <si>
     <t>Anna</t>
   </si>
   <si>
+    <t>07/10/1992</t>
+  </si>
+  <si>
     <t>Arménie</t>
   </si>
   <si>
+    <t>20/03/2025</t>
+  </si>
+  <si>
     <t>POGHOSYAN</t>
   </si>
   <si>
     <t>Gayane</t>
   </si>
   <si>
+    <t>25/09/1960</t>
+  </si>
+  <si>
+    <t>27/09/2023</t>
+  </si>
+  <si>
     <t>SAYED</t>
   </si>
   <si>
     <t>Mohammad</t>
   </si>
   <si>
+    <t>05/08/1989</t>
+  </si>
+  <si>
     <t>Allemagne</t>
   </si>
   <si>
+    <t>16/09/2025</t>
+  </si>
+  <si>
     <t>Tamara</t>
   </si>
   <si>
+    <t>24/07/1985</t>
+  </si>
+  <si>
     <t>YELEJYAN</t>
   </si>
   <si>
     <t>Gohar</t>
+  </si>
+  <si>
+    <t>20/12/1983</t>
+  </si>
+  <si>
+    <t>03/09/2025</t>
   </si>
 </sst>
 </file>
@@ -682,10 +727,10 @@
         <v>13</v>
       </c>
       <c r="G4" s="13" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="39.950000000000003" customHeight="1">
@@ -693,25 +738,25 @@
         <v>2</v>
       </c>
       <c r="B5" s="9" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C5" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="D5" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="D5" s="13" t="s">
-        <v>11</v>
-      </c>
       <c r="E5" s="2" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="F5" s="13" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="G5" s="13" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="39.950000000000003" customHeight="1">
@@ -719,13 +764,13 @@
         <v>3</v>
       </c>
       <c r="B6" s="9" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C6" s="11" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="D6" s="13" t="s">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>12</v>
@@ -734,10 +779,10 @@
         <v>13</v>
       </c>
       <c r="G6" s="13" t="s">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="39.950000000000003" customHeight="1">
@@ -745,25 +790,25 @@
         <v>4</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="C7" s="11" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="D7" s="13" t="s">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="F7" s="13" t="s">
         <v>13</v>
       </c>
       <c r="G7" s="13" t="s">
-        <v>11</v>
+        <v>28</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
     </row>
     <row r="8" spans="1:8" ht="39.950000000000003" customHeight="1">
@@ -771,25 +816,25 @@
         <v>5</v>
       </c>
       <c r="B8" s="9" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="C8" s="11" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="D8" s="13" t="s">
-        <v>11</v>
+        <v>31</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="F8" s="13" t="s">
         <v>13</v>
       </c>
       <c r="G8" s="13" t="s">
-        <v>11</v>
+        <v>33</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
     </row>
     <row r="9" spans="1:8" ht="39.950000000000003" customHeight="1">
@@ -797,25 +842,25 @@
         <v>6</v>
       </c>
       <c r="B9" s="9" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="C9" s="11" t="s">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="D9" s="13" t="s">
-        <v>11</v>
+        <v>36</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="F9" s="13" t="s">
         <v>13</v>
       </c>
       <c r="G9" s="13" t="s">
-        <v>11</v>
+        <v>37</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
     </row>
     <row r="10" spans="1:8" ht="39.950000000000003" customHeight="1">
@@ -823,25 +868,25 @@
         <v>7</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="C10" s="11" t="s">
-        <v>29</v>
+        <v>39</v>
       </c>
       <c r="D10" s="13" t="s">
-        <v>11</v>
+        <v>40</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>30</v>
+        <v>41</v>
       </c>
       <c r="F10" s="13" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="G10" s="13" t="s">
-        <v>11</v>
+        <v>42</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
     </row>
     <row r="11" spans="1:8" ht="39.950000000000003" customHeight="1">
@@ -849,25 +894,25 @@
         <v>8</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="C11" s="11" t="s">
-        <v>31</v>
+        <v>43</v>
       </c>
       <c r="D11" s="13" t="s">
-        <v>11</v>
+        <v>44</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>30</v>
+        <v>41</v>
       </c>
       <c r="F11" s="13" t="s">
         <v>13</v>
       </c>
       <c r="G11" s="13" t="s">
-        <v>11</v>
+        <v>42</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
     </row>
     <row r="12" spans="1:8" ht="39.950000000000003" customHeight="1">
@@ -875,25 +920,25 @@
         <v>9</v>
       </c>
       <c r="B12" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="C12" s="11" t="s">
+        <v>46</v>
+      </c>
+      <c r="D12" s="13" t="s">
+        <v>47</v>
+      </c>
+      <c r="E12" s="2" t="s">
         <v>32</v>
-      </c>
-      <c r="C12" s="11" t="s">
-        <v>33</v>
-      </c>
-      <c r="D12" s="13" t="s">
-        <v>11</v>
-      </c>
-      <c r="E12" s="2" t="s">
-        <v>25</v>
       </c>
       <c r="F12" s="13" t="s">
         <v>13</v>
       </c>
       <c r="G12" s="13" t="s">
-        <v>11</v>
+        <v>48</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
     </row>
     <row r="13" spans="1:8" ht="39.950000000000003" customHeight="1">
